--- a/20260929_株式会社チェングロウス御中_LINEOA施策提案【SIM】ver2.7.xlsx
+++ b/20260929_株式会社チェングロウス御中_LINEOA施策提案【SIM】ver2.7.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tonomura-r\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8A8E6F0-AEE8-491F-91CC-EABCAD1B2B54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B231411-FFC9-49F9-9C85-039C74AB730D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15420" yWindow="-16350" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SIM3_LINE登録2%" sheetId="1" r:id="rId1"/>
     <sheet name="SIM3_比較" sheetId="2" r:id="rId2"/>
     <sheet name="SIM考え方" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1" calcId="191029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1506,34 +1506,34 @@
         </ext>
       </extLst>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1985,7 +1985,7 @@
       </c>
     </row>
     <row r="8" spans="1:25" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A8" s="135" t="s">
+      <c r="A8" s="141" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="19" t="s">
@@ -2018,7 +2018,7 @@
       </c>
     </row>
     <row r="9" spans="1:25" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A9" s="136"/>
+      <c r="A9" s="139"/>
       <c r="B9" s="19" t="s">
         <v>14</v>
       </c>
@@ -2048,7 +2048,7 @@
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="135" t="s">
+      <c r="A10" s="141" t="s">
         <v>19</v>
       </c>
       <c r="B10" s="19" t="s">
@@ -2074,7 +2074,7 @@
       </c>
     </row>
     <row r="11" spans="1:25" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A11" s="136"/>
+      <c r="A11" s="139"/>
       <c r="B11" s="19" t="s">
         <v>24</v>
       </c>
@@ -2106,10 +2106,10 @@
       <c r="V12" s="55"/>
     </row>
     <row r="13" spans="1:25" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="145" t="s">
+      <c r="A13" s="146" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="138"/>
+      <c r="B13" s="136"/>
       <c r="C13" s="92"/>
       <c r="D13" s="13" t="s">
         <v>28</v>
@@ -2185,7 +2185,7 @@
       <c r="L14" s="7"/>
     </row>
     <row r="15" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="141"/>
+      <c r="A15" s="140"/>
       <c r="B15" s="20" t="s">
         <v>41</v>
       </c>
@@ -2228,7 +2228,7 @@
       </c>
     </row>
     <row r="16" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="136"/>
+      <c r="A16" s="139"/>
       <c r="B16" s="20" t="s">
         <v>45</v>
       </c>
@@ -2316,7 +2316,7 @@
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="141"/>
+      <c r="A18" s="140"/>
       <c r="B18" s="8" t="s">
         <v>54</v>
       </c>
@@ -2380,7 +2380,7 @@
       </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="141"/>
+      <c r="A19" s="140"/>
       <c r="B19" s="8" t="s">
         <v>57</v>
       </c>
@@ -2441,7 +2441,7 @@
       </c>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="141"/>
+      <c r="A20" s="140"/>
       <c r="B20" s="8" t="s">
         <v>59</v>
       </c>
@@ -2476,7 +2476,7 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="136"/>
+      <c r="A21" s="139"/>
       <c r="B21" s="8" t="s">
         <v>60</v>
       </c>
@@ -2519,7 +2519,7 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="140" t="s">
+      <c r="A22" s="143" t="s">
         <v>62</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -2571,7 +2571,7 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="141"/>
+      <c r="A23" s="140"/>
       <c r="B23" s="6" t="s">
         <v>54</v>
       </c>
@@ -2585,23 +2585,23 @@
       </c>
       <c r="F23" s="46">
         <f>IF(F18=FALSE,0,F14*0.4*0.125*0.125*0.81)</f>
-        <v>30.942</v>
+        <v>30.942000000000004</v>
       </c>
       <c r="G23" s="61">
         <f>IF(G18=FALSE,0,G14*0.4*0.125*0.125*0.93)</f>
-        <v>35.258625</v>
+        <v>35.258625000000002</v>
       </c>
       <c r="H23" s="61">
         <f>IF(H18=FALSE,0,H14*0.4*0.125*0.125*1)</f>
-        <v>38.61875</v>
+        <v>38.618750000000006</v>
       </c>
       <c r="I23" s="61">
         <f>IF(I18=FALSE,0,I14*0.4*0.125*0.125*1.03)</f>
-        <v>38.6571875</v>
+        <v>38.657187499999999</v>
       </c>
       <c r="J23" s="61">
         <f>IF(J18=FALSE,0,J14*0.4*0.125*0.125*1.05)</f>
-        <v>40.9696875</v>
+        <v>40.969687500000006</v>
       </c>
       <c r="K23" s="11"/>
       <c r="L23" s="7"/>
@@ -2624,7 +2624,7 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="141"/>
+      <c r="A24" s="140"/>
       <c r="B24" s="6" t="s">
         <v>57</v>
       </c>
@@ -2677,7 +2677,7 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="136"/>
+      <c r="A25" s="139"/>
       <c r="B25" s="6" t="s">
         <v>70</v>
       </c>
@@ -2728,22 +2728,22 @@
       <c r="A26" s="137" t="s">
         <v>73</v>
       </c>
-      <c r="B26" s="138"/>
+      <c r="B26" s="136"/>
       <c r="C26" s="23"/>
       <c r="D26" s="44" t="s">
         <v>50</v>
       </c>
       <c r="E26" s="46">
         <f>SUM(E22:E25)+E14*0.01*0.62</f>
-        <v>62.535525</v>
+        <v>62.535525000000007</v>
       </c>
       <c r="F26" s="46">
         <f>SUM(F22:F25)+F14*0.01*0.81</f>
-        <v>80.4492</v>
+        <v>80.449200000000005</v>
       </c>
       <c r="G26" s="46">
         <f>SUM(G22:G25)+G14*0.01*0.93</f>
-        <v>91.672425</v>
+        <v>91.672425000000004</v>
       </c>
       <c r="H26" s="46">
         <f>SUM(H22:H25)+H14*0.01*1</f>
@@ -2751,11 +2751,11 @@
       </c>
       <c r="I26" s="46">
         <f>SUM(I22:I25)+I14*0.01*1.03</f>
-        <v>100.5086875</v>
+        <v>100.50868750000001</v>
       </c>
       <c r="J26" s="46">
         <f>SUM(J22:J25)+J14*0.01*1.05</f>
-        <v>106.5211875</v>
+        <v>106.52118750000001</v>
       </c>
       <c r="K26" s="11"/>
       <c r="L26" s="7"/>
@@ -2778,7 +2778,7 @@
       <c r="A27" s="137" t="s">
         <v>75</v>
       </c>
-      <c r="B27" s="138"/>
+      <c r="B27" s="136"/>
       <c r="C27" s="23"/>
       <c r="D27" s="104">
         <v>0</v>
@@ -2822,37 +2822,37 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="144" t="s">
+      <c r="A28" s="145" t="s">
         <v>77</v>
       </c>
-      <c r="B28" s="138"/>
+      <c r="B28" s="136"/>
       <c r="C28" s="98"/>
       <c r="D28" s="103">
         <v>0</v>
       </c>
       <c r="E28" s="49">
         <f t="shared" ref="E28:J28" si="0">+D28+E26</f>
-        <v>62.535525</v>
+        <v>62.535525000000007</v>
       </c>
       <c r="F28" s="49">
         <f t="shared" si="0"/>
-        <v>142.984725</v>
+        <v>142.98472500000003</v>
       </c>
       <c r="G28" s="49">
         <f t="shared" si="0"/>
-        <v>234.65715</v>
+        <v>234.65715000000003</v>
       </c>
       <c r="H28" s="49">
         <f t="shared" si="0"/>
-        <v>335.0659</v>
+        <v>335.06590000000006</v>
       </c>
       <c r="I28" s="49">
         <f t="shared" si="0"/>
-        <v>435.5745875</v>
+        <v>435.57458750000006</v>
       </c>
       <c r="J28" s="49">
         <f t="shared" si="0"/>
-        <v>542.095775</v>
+        <v>542.09577500000012</v>
       </c>
       <c r="K28" s="12"/>
       <c r="L28" s="7"/>
@@ -2872,37 +2872,37 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="142" t="s">
+      <c r="A29" s="144" t="s">
         <v>78</v>
       </c>
-      <c r="B29" s="138"/>
+      <c r="B29" s="136"/>
       <c r="C29" s="99"/>
       <c r="D29" s="105">
         <v>0</v>
       </c>
       <c r="E29" s="50">
         <f t="shared" ref="E29:J29" si="1">+E28*(1-E27)</f>
-        <v>37.14610185</v>
+        <v>37.146101850000001</v>
       </c>
       <c r="F29" s="50">
         <f t="shared" si="1"/>
-        <v>87.077697525</v>
+        <v>87.077697525000019</v>
       </c>
       <c r="G29" s="50">
         <f t="shared" si="1"/>
-        <v>145.9567473</v>
+        <v>145.95674730000002</v>
       </c>
       <c r="H29" s="50">
         <f t="shared" si="1"/>
-        <v>213.7720442</v>
+        <v>213.77204420000004</v>
       </c>
       <c r="I29" s="50">
         <f t="shared" si="1"/>
-        <v>279.2033105875</v>
+        <v>279.20331058750003</v>
       </c>
       <c r="J29" s="50">
         <f t="shared" si="1"/>
-        <v>355.6148284</v>
+        <v>355.61482840000008</v>
       </c>
       <c r="K29" s="12"/>
       <c r="L29" s="7"/>
@@ -2916,10 +2916,10 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="139" t="s">
+      <c r="A30" s="142" t="s">
         <v>80</v>
       </c>
-      <c r="B30" s="138"/>
+      <c r="B30" s="136"/>
       <c r="C30" s="30"/>
       <c r="D30" s="48">
         <v>0</v>
@@ -2961,7 +2961,7 @@
       <c r="A31" s="137" t="s">
         <v>83</v>
       </c>
-      <c r="B31" s="138"/>
+      <c r="B31" s="136"/>
       <c r="C31" s="23"/>
       <c r="D31" s="105">
         <f>+D30*D29*0.41*0.07</f>
@@ -2969,27 +2969,27 @@
       </c>
       <c r="E31" s="61">
         <f>+E29*E30*$P$24*$P$22*$P$23*$P$36</f>
-        <v>13.5746476865588</v>
+        <v>13.574647686558823</v>
       </c>
       <c r="F31" s="61">
         <f>+F29*F30*$P$24*$P$22*$P$23*$P$36</f>
-        <v>31.8216180538096</v>
+        <v>31.821618053809608</v>
       </c>
       <c r="G31" s="61">
         <f>+G29*G30*$P$24*$P$22*$P$23*$P$36</f>
-        <v>53.3383403209938</v>
+        <v>53.338340320993758</v>
       </c>
       <c r="H31" s="61">
         <f>+H29*H30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
-        <v>62.4965752146718</v>
+        <v>62.496575214671829</v>
       </c>
       <c r="I31" s="61">
         <f>+I29*I30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
-        <v>81.6255033047818</v>
+        <v>81.62550330478183</v>
       </c>
       <c r="J31" s="61">
         <f>+J29*J30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
-        <v>103.964524237605</v>
+        <v>103.96452423760475</v>
       </c>
       <c r="K31" s="11"/>
       <c r="L31" s="7"/>
@@ -3000,10 +3000,10 @@
       <c r="Z31" s="35"/>
     </row>
     <row r="32" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="139" t="s">
+      <c r="A32" s="142" t="s">
         <v>84</v>
       </c>
-      <c r="B32" s="138"/>
+      <c r="B32" s="136"/>
       <c r="C32" s="30"/>
       <c r="D32" s="48">
         <v>0</v>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="Q32" s="71">
         <f>+IF(P32=TRUE,1.1,0.95)</f>
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="S32" s="34"/>
       <c r="U32" s="34"/>
@@ -3050,34 +3050,34 @@
       <c r="A33" s="137" t="s">
         <v>87</v>
       </c>
-      <c r="B33" s="138"/>
+      <c r="B33" s="136"/>
       <c r="C33" s="23"/>
       <c r="D33" s="44">
         <v>0</v>
       </c>
       <c r="E33" s="61">
         <f>+E29*E32*$P$26*$P$27*$P$28*$P$36</f>
-        <v>9.46309574303379</v>
+        <v>9.4630957430337936</v>
       </c>
       <c r="F33" s="61">
         <f>+F29*F32*$P$26*$P$27*$P$28*$P$36</f>
-        <v>22.1833395086653</v>
+        <v>22.183339508665348</v>
       </c>
       <c r="G33" s="61">
         <f>+G29*G32*$P$26*$P$27*$P$28*$P$36</f>
-        <v>37.1829776276158</v>
+        <v>37.182977627615841</v>
       </c>
       <c r="H33" s="61">
         <f>+H29*H32*$P$26*$P$27*$P$28*$P$36*$Q$28</f>
-        <v>43.5673240679203</v>
+        <v>43.567324067920254</v>
       </c>
       <c r="I33" s="61">
         <f>+I29*I32*$P$26*$P$27*$P$28*$P$36*$Q$28</f>
-        <v>56.9023941307373</v>
+        <v>56.902394130737321</v>
       </c>
       <c r="J33" s="61">
         <f>+J29*J32*$P$26*$P$27*$P$28*$P$36*$Q$28</f>
-        <v>72.4752693002533</v>
+        <v>72.475269300253288</v>
       </c>
       <c r="K33" s="11"/>
       <c r="L33" s="7"/>
@@ -3089,14 +3089,14 @@
       </c>
       <c r="Q33" s="71">
         <f>+IF(P33=TRUE,1.1,0.95)</f>
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="142" t="s">
+      <c r="A34" s="144" t="s">
         <v>89</v>
       </c>
-      <c r="B34" s="138"/>
+      <c r="B34" s="136"/>
       <c r="C34" s="99"/>
       <c r="D34" s="105">
         <f>+D29*D30</f>
@@ -3104,27 +3104,27 @@
       </c>
       <c r="E34" s="46">
         <f>+E29*E30*$P$24+E29*E32*$P$28</f>
-        <v>193.15972962</v>
+        <v>193.15972962000001</v>
       </c>
       <c r="F34" s="46">
         <f>+F29*F30*$P$24+F29*F32*$P$28</f>
-        <v>452.80402713</v>
+        <v>452.80402713000012</v>
       </c>
       <c r="G34" s="46">
         <f>+G29*G30*$P$24+G29*G32*$P$28</f>
-        <v>758.97508596</v>
+        <v>758.97508596000011</v>
       </c>
       <c r="H34" s="46">
         <f>+H29*H30*$P$24*$Q$24+H29*H32*$P$28*$Q$28</f>
-        <v>889.291703872</v>
+        <v>889.2917038720002</v>
       </c>
       <c r="I34" s="46">
         <f>+I29*I30*$P$24*$Q$24+I29*I32*$P$28*$Q$28</f>
-        <v>1161.485772044</v>
+        <v>1161.4857720440002</v>
       </c>
       <c r="J34" s="46">
         <f>+J29*J30*$P$24*$Q$24+J29*J32*$P$28*$Q$28</f>
-        <v>1479.357686144</v>
+        <v>1479.3576861440006</v>
       </c>
       <c r="K34" s="11"/>
       <c r="L34" s="7"/>
@@ -3136,14 +3136,14 @@
       </c>
       <c r="Q34" s="71">
         <f>+IF(P34=TRUE,1.1,0.95)</f>
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="142" t="s">
+      <c r="A35" s="144" t="s">
         <v>91</v>
       </c>
-      <c r="B35" s="138"/>
+      <c r="B35" s="136"/>
       <c r="C35" s="99"/>
       <c r="D35" s="106">
         <f>+D31*1.02</f>
@@ -3151,27 +3151,27 @@
       </c>
       <c r="E35" s="50">
         <f t="shared" ref="E35:J35" si="2">+E31+E33+1.05*(E31+E33)+E29*0.3*2</f>
-        <v>69.5150351406649</v>
+        <v>69.515035140664864</v>
       </c>
       <c r="F35" s="50">
         <f t="shared" si="2"/>
-        <v>162.956781518074</v>
+        <v>162.95678151807368</v>
       </c>
       <c r="G35" s="50">
         <f t="shared" si="2"/>
-        <v>273.14275017465</v>
+        <v>273.14275017464973</v>
       </c>
       <c r="H35" s="50">
         <f t="shared" si="2"/>
-        <v>345.694220049314</v>
+        <v>345.6942200493138</v>
       </c>
       <c r="I35" s="50">
         <f t="shared" si="2"/>
-        <v>451.504176095314</v>
+        <v>451.50417609531428</v>
       </c>
       <c r="J35" s="50">
         <f t="shared" si="2"/>
-        <v>575.070473792609</v>
+        <v>575.07047379260894</v>
       </c>
       <c r="K35" s="11"/>
       <c r="L35" s="7"/>
@@ -3186,11 +3186,11 @@
       </c>
       <c r="Q35" s="71">
         <f>+IF(P35=TRUE,1.1,0.95)</f>
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="143" t="s">
+      <c r="A36" s="138" t="s">
         <v>7</v>
       </c>
       <c r="B36" s="6" t="str">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="P36" s="72">
         <f>1*(Q32*Q33*Q34*Q35)</f>
-        <v>1.4641</v>
+        <v>1.4641000000000006</v>
       </c>
       <c r="Q36" s="71"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="136"/>
+      <c r="A37" s="139"/>
       <c r="B37" s="6" t="str">
         <f>+C9</f>
         <v>求人応募（LINE経由）</v>
@@ -3256,23 +3256,23 @@
         <v>3</v>
       </c>
       <c r="F37" s="108">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G37" s="108">
         <v>8</v>
       </c>
       <c r="H37" s="108">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I37" s="108">
+        <v>12</v>
+      </c>
+      <c r="J37" s="108">
         <v>13</v>
-      </c>
-      <c r="J37" s="108">
-        <v>15</v>
       </c>
       <c r="K37" s="112">
         <f>SUM(E37:J37)</f>
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="L37" s="7"/>
       <c r="N37" s="67" t="s">
@@ -3280,7 +3280,7 @@
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="143" t="s">
+      <c r="A38" s="138" t="s">
         <v>19</v>
       </c>
       <c r="B38" s="6" t="str">
@@ -3322,7 +3322,7 @@
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="136"/>
+      <c r="A39" s="139"/>
       <c r="B39" s="6" t="str">
         <f>+C11</f>
         <v>-</v>
@@ -3362,10 +3362,10 @@
       </c>
     </row>
     <row r="40" spans="1:17" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="135" t="s">
+      <c r="A40" s="141" t="s">
         <v>100</v>
       </c>
-      <c r="B40" s="138"/>
+      <c r="B40" s="136"/>
       <c r="C40" s="94"/>
       <c r="D40" s="11">
         <f t="shared" ref="D40:J40" si="3">+D37</f>
@@ -3377,7 +3377,7 @@
       </c>
       <c r="F40" s="10">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G40" s="10">
         <f t="shared" si="3"/>
@@ -3385,19 +3385,19 @@
       </c>
       <c r="H40" s="10">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I40" s="10">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J40" s="10">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K40" s="112">
         <f>SUM(E40:J40)</f>
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="L40" s="7"/>
       <c r="N40" t="s">
@@ -3415,27 +3415,27 @@
       </c>
       <c r="E41" s="18">
         <f t="shared" si="4"/>
-        <v>0.043156131532257</v>
+        <v>4.3156131532256996E-2</v>
       </c>
       <c r="F41" s="18">
         <f t="shared" si="4"/>
-        <v>0.0306829820362244</v>
+        <v>3.6819578443469288E-2</v>
       </c>
       <c r="G41" s="18">
         <f t="shared" si="4"/>
-        <v>0.0292887143989168</v>
+        <v>2.9288714398916806E-2</v>
       </c>
       <c r="H41" s="18">
         <f t="shared" si="4"/>
-        <v>0.0318200286901842</v>
+        <v>2.8927298809258324E-2</v>
       </c>
       <c r="I41" s="18">
         <f t="shared" si="4"/>
-        <v>0.0287926461997013</v>
+        <v>2.6577827261262704E-2</v>
       </c>
       <c r="J41" s="18">
         <f t="shared" si="4"/>
-        <v>0.0260837596148425</v>
+        <v>2.2605924999530173E-2</v>
       </c>
       <c r="N41" s="67" t="s">
         <v>103</v>
@@ -3466,7 +3466,7 @@
       <c r="A44" s="137" t="s">
         <v>107</v>
       </c>
-      <c r="B44" s="138"/>
+      <c r="B44" s="136"/>
       <c r="C44" s="100"/>
       <c r="D44" s="16" t="s">
         <v>50</v>
@@ -3502,7 +3502,7 @@
       <c r="A45" s="137" t="s">
         <v>108</v>
       </c>
-      <c r="B45" s="138"/>
+      <c r="B45" s="136"/>
       <c r="C45" s="101">
         <f>+SUM(C65:C72)</f>
         <v>0</v>
@@ -3542,34 +3542,34 @@
       <c r="A46" s="137" t="s">
         <v>109</v>
       </c>
-      <c r="B46" s="138"/>
+      <c r="B46" s="136"/>
       <c r="C46" s="100"/>
       <c r="D46" s="16" t="s">
         <v>50</v>
       </c>
       <c r="E46" s="28">
         <f t="shared" ref="E46:J46" si="7">+SUM(E65:E67)/(E28-D28)</f>
-        <v>479.727322989613</v>
+        <v>479.72732298961267</v>
       </c>
       <c r="F46" s="28">
         <f t="shared" si="7"/>
-        <v>372.906132068436</v>
+        <v>372.90613206843562</v>
       </c>
       <c r="G46" s="28">
         <f t="shared" si="7"/>
-        <v>327.252169886419</v>
+        <v>327.25216988641893</v>
       </c>
       <c r="H46" s="28">
         <f t="shared" si="7"/>
-        <v>298.778741892514</v>
+        <v>298.77874189251429</v>
       </c>
       <c r="I46" s="28">
         <f t="shared" si="7"/>
-        <v>298.481661100191</v>
+        <v>298.48166110019093</v>
       </c>
       <c r="J46" s="28">
         <f t="shared" si="7"/>
-        <v>281.634111523588</v>
+        <v>281.63411152358759</v>
       </c>
       <c r="K46" s="11"/>
       <c r="L46" s="7"/>
@@ -3578,34 +3578,34 @@
       <c r="A47" s="137" t="s">
         <v>110</v>
       </c>
-      <c r="B47" s="138"/>
+      <c r="B47" s="136"/>
       <c r="C47" s="100"/>
       <c r="D47" s="16" t="s">
         <v>50</v>
       </c>
       <c r="E47" s="28">
         <f t="shared" ref="E47:J47" si="8">+E51/E35</f>
-        <v>3380.56363669346</v>
+        <v>3380.5636366934646</v>
       </c>
       <c r="F47" s="28">
         <f t="shared" si="8"/>
-        <v>1442.10015570255</v>
+        <v>1442.100155702547</v>
       </c>
       <c r="G47" s="28">
         <f t="shared" si="8"/>
-        <v>860.355985468181</v>
+        <v>860.35598546818119</v>
       </c>
       <c r="H47" s="28">
         <f t="shared" si="8"/>
-        <v>679.791522017571</v>
+        <v>679.79152201757063</v>
       </c>
       <c r="I47" s="28">
         <f t="shared" si="8"/>
-        <v>520.482450533061</v>
+        <v>520.4824505330613</v>
       </c>
       <c r="J47" s="28">
         <f t="shared" si="8"/>
-        <v>408.645567299199</v>
+        <v>408.64556729919929</v>
       </c>
       <c r="K47" s="11"/>
       <c r="L47" s="7"/>
@@ -3614,54 +3614,54 @@
       <c r="A48" s="137" t="s">
         <v>111</v>
       </c>
-      <c r="B48" s="138"/>
+      <c r="B48" s="136"/>
       <c r="C48" s="100"/>
       <c r="D48" s="16" t="s">
         <v>50</v>
       </c>
       <c r="E48" s="32">
         <f t="shared" ref="E48:J48" si="9">+SUM(E36:E39)/E35</f>
-        <v>0.589800464274179</v>
+        <v>0.58980046427417898</v>
       </c>
       <c r="F48" s="32">
         <f t="shared" si="9"/>
-        <v>0.337512802398469</v>
+        <v>0.34364939880571332</v>
       </c>
       <c r="G48" s="32">
         <f t="shared" si="9"/>
-        <v>0.234309715191334</v>
+        <v>0.23430971519133445</v>
       </c>
       <c r="H48" s="32">
         <f t="shared" si="9"/>
-        <v>0.211169281307586</v>
+        <v>0.20827655142665993</v>
       </c>
       <c r="I48" s="32">
         <f t="shared" si="9"/>
-        <v>0.166111420382892</v>
+        <v>0.16389660144445334</v>
       </c>
       <c r="J48" s="32">
         <f t="shared" si="9"/>
-        <v>0.14085230192015</v>
+        <v>0.13737446730483721</v>
       </c>
       <c r="K48" s="11"/>
       <c r="L48" s="7"/>
     </row>
     <row r="49" spans="1:12" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="135" t="s">
+      <c r="A49" s="141" t="s">
         <v>112</v>
       </c>
-      <c r="B49" s="138"/>
+      <c r="B49" s="136"/>
       <c r="C49" s="102"/>
       <c r="D49" s="16" t="s">
         <v>50</v>
       </c>
       <c r="E49" s="28">
         <f>+IFERROR(E51/SUM(E37:E39),0)</f>
-        <v>78333.3333333333</v>
+        <v>78333.333333333328</v>
       </c>
       <c r="F49" s="28">
         <f t="shared" ref="F49:J49" si="10">+IFERROR(F51/SUM(F37:F39),0)</f>
-        <v>47000</v>
+        <v>39166.666666666664</v>
       </c>
       <c r="G49" s="28">
         <f t="shared" si="10"/>
@@ -3669,24 +3669,24 @@
       </c>
       <c r="H49" s="28">
         <f t="shared" si="10"/>
-        <v>21363.6363636364</v>
+        <v>23500</v>
       </c>
       <c r="I49" s="28">
         <f t="shared" si="10"/>
-        <v>18076.9230769231</v>
+        <v>19583.333333333332</v>
       </c>
       <c r="J49" s="28">
         <f t="shared" si="10"/>
-        <v>15666.6666666667</v>
+        <v>18076.923076923078</v>
       </c>
       <c r="K49" s="11"/>
       <c r="L49" s="7"/>
     </row>
     <row r="50" spans="1:12" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="135" t="s">
+      <c r="A50" s="141" t="s">
         <v>113</v>
       </c>
-      <c r="B50" s="138"/>
+      <c r="B50" s="136"/>
       <c r="C50" s="102"/>
       <c r="D50" s="62" t="s">
         <v>50</v>
@@ -3719,10 +3719,10 @@
       <c r="L50" s="7"/>
     </row>
     <row r="51" spans="1:12" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="146" t="s">
+      <c r="A51" s="135" t="s">
         <v>114</v>
       </c>
-      <c r="B51" s="138"/>
+      <c r="B51" s="136"/>
       <c r="C51" s="107">
         <f>+C45</f>
         <v>0</v>
@@ -3779,7 +3779,7 @@
       <c r="A54" s="137" t="s">
         <v>107</v>
       </c>
-      <c r="B54" s="138"/>
+      <c r="B54" s="136"/>
       <c r="C54" s="93"/>
       <c r="D54" s="28">
         <f t="shared" ref="D54:J54" si="13">+D75*D76</f>
@@ -3816,7 +3816,7 @@
       <c r="A55" s="137" t="s">
         <v>108</v>
       </c>
-      <c r="B55" s="138"/>
+      <c r="B55" s="136"/>
       <c r="C55" s="93"/>
       <c r="D55" s="27">
         <f>+SUM(D65:D72)</f>
@@ -3853,34 +3853,34 @@
       <c r="A56" s="137" t="s">
         <v>109</v>
       </c>
-      <c r="B56" s="138"/>
+      <c r="B56" s="136"/>
       <c r="C56" s="93"/>
       <c r="D56" s="39" t="s">
         <v>50</v>
       </c>
       <c r="E56" s="28">
         <f t="shared" ref="E56:J56" si="15">+SUM(E65:E67)/(E28-D28)</f>
-        <v>479.727322989613</v>
+        <v>479.72732298961267</v>
       </c>
       <c r="F56" s="28">
         <f t="shared" si="15"/>
-        <v>372.906132068436</v>
+        <v>372.90613206843562</v>
       </c>
       <c r="G56" s="28">
         <f t="shared" si="15"/>
-        <v>327.252169886419</v>
+        <v>327.25216988641893</v>
       </c>
       <c r="H56" s="28">
         <f t="shared" si="15"/>
-        <v>298.778741892514</v>
+        <v>298.77874189251429</v>
       </c>
       <c r="I56" s="28">
         <f t="shared" si="15"/>
-        <v>298.481661100191</v>
+        <v>298.48166110019093</v>
       </c>
       <c r="J56" s="28">
         <f t="shared" si="15"/>
-        <v>281.634111523588</v>
+        <v>281.63411152358759</v>
       </c>
       <c r="K56" s="11"/>
       <c r="L56" s="7"/>
@@ -3889,34 +3889,34 @@
       <c r="A57" s="137" t="s">
         <v>110</v>
       </c>
-      <c r="B57" s="138"/>
+      <c r="B57" s="136"/>
       <c r="C57" s="93"/>
       <c r="D57" s="39" t="s">
         <v>50</v>
       </c>
       <c r="E57" s="28">
         <f t="shared" ref="E57:J57" si="16">+E61/E35</f>
-        <v>3380.56363669346</v>
+        <v>3380.5636366934646</v>
       </c>
       <c r="F57" s="28">
         <f t="shared" si="16"/>
-        <v>1442.10015570255</v>
+        <v>1442.100155702547</v>
       </c>
       <c r="G57" s="28">
         <f t="shared" si="16"/>
-        <v>860.355985468181</v>
+        <v>860.35598546818119</v>
       </c>
       <c r="H57" s="28">
         <f t="shared" si="16"/>
-        <v>679.791522017571</v>
+        <v>679.79152201757063</v>
       </c>
       <c r="I57" s="28">
         <f t="shared" si="16"/>
-        <v>520.482450533061</v>
+        <v>520.4824505330613</v>
       </c>
       <c r="J57" s="28">
         <f t="shared" si="16"/>
-        <v>408.645567299199</v>
+        <v>408.64556729919929</v>
       </c>
       <c r="K57" s="11"/>
       <c r="L57" s="7"/>
@@ -3925,52 +3925,52 @@
       <c r="A58" s="137" t="s">
         <v>111</v>
       </c>
-      <c r="B58" s="138"/>
+      <c r="B58" s="136"/>
       <c r="C58" s="93"/>
       <c r="D58" s="39" t="s">
         <v>50</v>
       </c>
       <c r="E58" s="32">
         <f t="shared" ref="E58:J58" si="17">+SUM(E36:E39)/E35</f>
-        <v>0.589800464274179</v>
+        <v>0.58980046427417898</v>
       </c>
       <c r="F58" s="32">
         <f t="shared" si="17"/>
-        <v>0.337512802398469</v>
+        <v>0.34364939880571332</v>
       </c>
       <c r="G58" s="32">
         <f t="shared" si="17"/>
-        <v>0.234309715191334</v>
+        <v>0.23430971519133445</v>
       </c>
       <c r="H58" s="32">
         <f t="shared" si="17"/>
-        <v>0.211169281307586</v>
+        <v>0.20827655142665993</v>
       </c>
       <c r="I58" s="32">
         <f t="shared" si="17"/>
-        <v>0.166111420382892</v>
+        <v>0.16389660144445334</v>
       </c>
       <c r="J58" s="32">
         <f t="shared" si="17"/>
-        <v>0.14085230192015</v>
+        <v>0.13737446730483721</v>
       </c>
       <c r="K58" s="11"/>
       <c r="L58" s="7"/>
     </row>
     <row r="59" spans="1:12" ht="18" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="135" t="s">
+      <c r="A59" s="141" t="s">
         <v>112</v>
       </c>
-      <c r="B59" s="138"/>
+      <c r="B59" s="136"/>
       <c r="C59" s="94"/>
       <c r="D59" s="28"/>
       <c r="E59" s="28">
         <f t="shared" ref="E59:J59" si="18">+IFERROR(E55/E40,0)</f>
-        <v>78333.3333333333</v>
+        <v>78333.333333333328</v>
       </c>
       <c r="F59" s="28">
         <f t="shared" si="18"/>
-        <v>47000</v>
+        <v>39166.666666666664</v>
       </c>
       <c r="G59" s="28">
         <f t="shared" si="18"/>
@@ -3978,24 +3978,24 @@
       </c>
       <c r="H59" s="28">
         <f t="shared" si="18"/>
-        <v>21363.6363636364</v>
+        <v>23500</v>
       </c>
       <c r="I59" s="28">
         <f t="shared" si="18"/>
-        <v>18076.9230769231</v>
+        <v>19583.333333333332</v>
       </c>
       <c r="J59" s="28">
         <f t="shared" si="18"/>
-        <v>15666.6666666667</v>
+        <v>18076.923076923078</v>
       </c>
       <c r="K59" s="11"/>
       <c r="L59" s="7"/>
     </row>
     <row r="60" spans="1:12" ht="18" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="135" t="s">
+      <c r="A60" s="141" t="s">
         <v>113</v>
       </c>
-      <c r="B60" s="138"/>
+      <c r="B60" s="136"/>
       <c r="C60" s="94"/>
       <c r="D60" s="28"/>
       <c r="E60" s="28"/>
@@ -4008,10 +4008,10 @@
       <c r="L60" s="7"/>
     </row>
     <row r="61" spans="1:12" ht="18" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" s="146" t="s">
+      <c r="A61" s="135" t="s">
         <v>114</v>
       </c>
-      <c r="B61" s="138"/>
+      <c r="B61" s="136"/>
       <c r="C61" s="95"/>
       <c r="D61" s="40">
         <f>+D55</f>
@@ -4458,6 +4458,25 @@
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A44:B44"/>
     <mergeCell ref="A51:B51"/>
     <mergeCell ref="A45:B45"/>
     <mergeCell ref="A36:A37"/>
@@ -4474,25 +4493,6 @@
     <mergeCell ref="A58:B58"/>
     <mergeCell ref="A48:B48"/>
     <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A34:B34"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4588,11 +4588,11 @@
       </c>
       <c r="D6" s="84">
         <f>+'SIM3_LINE登録2%'!G28</f>
-        <v>234.65715</v>
+        <v>234.65715000000003</v>
       </c>
       <c r="E6" s="84">
         <f>+'SIM3_LINE登録2%'!J28</f>
-        <v>542.095775</v>
+        <v>542.09577500000012</v>
       </c>
       <c r="F6" s="10"/>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="E7" s="86">
         <f>'SIM3_LINE登録2%'!J27</f>
-        <v>0.344</v>
+        <v>0.34399999999999997</v>
       </c>
       <c r="F7" s="86"/>
     </row>
@@ -4626,11 +4626,11 @@
       </c>
       <c r="D8" s="10">
         <f>+'SIM3_LINE登録2%'!G29</f>
-        <v>145.9567473</v>
+        <v>145.95674730000002</v>
       </c>
       <c r="E8" s="10">
         <f>+'SIM3_LINE登録2%'!J29</f>
-        <v>355.6148284</v>
+        <v>355.61482840000008</v>
       </c>
       <c r="F8" s="10"/>
     </row>
@@ -4653,11 +4653,11 @@
       </c>
       <c r="D10" s="10">
         <f>+'SIM3_LINE登録2%'!G34</f>
-        <v>758.97508596</v>
+        <v>758.97508596000011</v>
       </c>
       <c r="E10" s="10">
         <f>+'SIM3_LINE登録2%'!J34</f>
-        <v>1479.357686144</v>
+        <v>1479.3576861440006</v>
       </c>
       <c r="F10" s="10"/>
     </row>
@@ -4672,11 +4672,11 @@
       </c>
       <c r="D11" s="10">
         <f>+'SIM3_LINE登録2%'!G35</f>
-        <v>273.14275017465</v>
+        <v>273.14275017464973</v>
       </c>
       <c r="E11" s="10">
         <f>+'SIM3_LINE登録2%'!J35</f>
-        <v>575.070473792609</v>
+        <v>575.07047379260894</v>
       </c>
       <c r="F11" s="10"/>
     </row>
@@ -4691,11 +4691,11 @@
       </c>
       <c r="D12" s="28">
         <f>+D4/D11</f>
-        <v>860.355985468181</v>
+        <v>860.35598546818119</v>
       </c>
       <c r="E12" s="28">
         <f>+E4/E11</f>
-        <v>408.645567299199</v>
+        <v>408.64556729919929</v>
       </c>
       <c r="F12" s="28"/>
     </row>
@@ -4710,11 +4710,11 @@
       </c>
       <c r="D13" s="28">
         <f>+D5/D11</f>
-        <v>860.355985468181</v>
+        <v>860.35598546818119</v>
       </c>
       <c r="E13" s="28">
         <f>+E5/E11</f>
-        <v>408.645567299199</v>
+        <v>408.64556729919929</v>
       </c>
       <c r="F13" s="28"/>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="E16" s="84">
         <f>+E18</f>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F16" s="84"/>
       <c r="R16" s="5" t="s">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="E18" s="84">
         <f>+'SIM3_LINE登録2%'!J37</f>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F18" s="10"/>
       <c r="R18" s="34">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="E22" s="87">
         <f>+IFERROR(E4/E16,"--")</f>
-        <v>15666.6666666667</v>
+        <v>18076.923076923078</v>
       </c>
       <c r="F22" s="87"/>
       <c r="R22" s="34"/>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="E23" s="87">
         <f>+IFERROR(E5/E16,"--")</f>
-        <v>15666.6666666667</v>
+        <v>18076.923076923078</v>
       </c>
       <c r="F23" s="87"/>
       <c r="R23" s="34"/>
